--- a/docs/seguimiento/03_Plan_Trabajo_Carta_Gantt_y_RACI_Fase2.xlsx
+++ b/docs/seguimiento/03_Plan_Trabajo_Carta_Gantt_y_RACI_Fase2.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt" sheetId="1" r:id="R090f338f308e4d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Trabajo" sheetId="2" r:id="Rd94981c20de74c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="3" r:id="R7bb7205b08034da5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RACI" sheetId="4" r:id="Rf70a396d0fa5403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="5" r:id="Rf688ce6bdf8d43d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control_Scrum_QA" sheetId="6" r:id="R3d10424c23fc49bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt" sheetId="1" r:id="R2542a7c01ddc44d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Trabajo" sheetId="2" r:id="Rb0e3aca3e3474f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="3" r:id="Rcfa7f1ccf97f45ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RACI" sheetId="4" r:id="R99b1f574467647f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="5" r:id="R9e49a5dd7400460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control_Scrum_QA" sheetId="6" r:id="R35aad0398f53466d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -369,9 +369,6 @@
     <x:t xml:space="preserve">2026-10-04</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Pruebas de endpoints</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Módulo de métricas</x:t>
   </x:si>
   <x:si>
@@ -381,9 +378,6 @@
     <x:t xml:space="preserve">Implementar gestión de patrocinadores</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Pruebas CRUD</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Módulo de patrocinadores</x:t>
   </x:si>
   <x:si>
@@ -501,9 +495,6 @@
     <x:t xml:space="preserve">Implementar listado y creación de preguntas</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Pruebas de preguntas</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Base de contenido</x:t>
   </x:si>
   <x:si>
@@ -541,9 +532,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2026-11-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pruebas de importación</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Módulo de preguntas</x:t>
@@ -1867,7 +1855,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="16" t="str">
-        <x:v>Fechas de línea base conservadas. Avance A al 29/09/2026; calendario no rebaselizado ni sprints aceptados.</x:v>
+        <x:v>Avance técnico al 20/10/2026. Fechas históricas y ceremonias no modificadas.</x:v>
       </x:c>
       <x:c r="B2" s="16"/>
       <x:c r="C2" s="16"/>
@@ -2638,7 +2626,7 @@
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="L14" s="22" t="str">
-        <x:v>Evidencias equipo-a; revisión de Felipe pendiente</x:v>
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M14" s="22" t="s">
         <x:v>101</x:v>
@@ -2706,7 +2694,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="N15" s="20" t="str">
-        <x:v>PARCIAL / A_VERIFICADO</x:v>
+        <x:v>REGRESION_LOCAL / ACEPTACION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O15" s="19"/>
       <x:c r="P15" s="19"/>
@@ -2823,14 +2811,14 @@
       <x:c r="K17" s="19" t="str">
         <x:v>Felipe</x:v>
       </x:c>
-      <x:c r="L17" s="19" t="s">
+      <x:c r="L17" s="19" t="str">
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
+      </x:c>
+      <x:c r="M17" s="19" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="M17" s="19" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="N17" s="20" t="s">
-        <x:v>42</x:v>
+      <x:c r="N17" s="20" t="str">
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O17" s="19"/>
       <x:c r="P17" s="19"/>
@@ -2853,10 +2841,10 @@
     </x:row>
     <x:row r="18" ht="27.950000762939453" customHeight="1">
       <x:c r="A18" s="22" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B18" s="22" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="C18" s="22" t="s">
         <x:v>92</x:v>
@@ -2885,14 +2873,14 @@
       <x:c r="K18" s="22" t="str">
         <x:v>Catalina</x:v>
       </x:c>
-      <x:c r="L18" s="22" t="s">
-        <x:v>122</x:v>
+      <x:c r="L18" s="22" t="str">
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M18" s="22" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="N18" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="N18" s="20" t="str">
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O18" s="19"/>
       <x:c r="P18" s="19"/>
@@ -2915,10 +2903,10 @@
     </x:row>
     <x:row r="19" ht="27.950000762939453" customHeight="1">
       <x:c r="A19" s="19" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B19" s="19" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C19" s="19" t="s">
         <x:v>68</x:v>
@@ -2939,7 +2927,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I19" s="19" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J19" s="19" t="s">
         <x:v>47</x:v>
@@ -2951,10 +2939,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="M19" s="19" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="N19" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="N19" s="20" t="str">
+        <x:v>REGRESION_LOCAL / ACEPTACION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O19" s="19"/>
       <x:c r="P19" s="19"/>
@@ -2977,10 +2965,10 @@
     </x:row>
     <x:row r="20" ht="27.950000762939453" customHeight="1">
       <x:c r="A20" s="22" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B20" s="22" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C20" s="22" t="s">
         <x:v>85</x:v>
@@ -2992,7 +2980,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="F20" s="22" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G20" s="22" t="s">
         <x:v>117</x:v>
@@ -3001,7 +2989,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="22" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J20" s="22" t="s">
         <x:v>88</x:v>
@@ -3013,7 +3001,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="M20" s="22" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="N20" s="20" t="s">
         <x:v>42</x:v>
@@ -3039,10 +3027,10 @@
     </x:row>
     <x:row r="21" ht="27.950000762939453" customHeight="1">
       <x:c r="A21" s="19" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B21" s="19" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C21" s="19" t="s">
         <x:v>92</x:v>
@@ -3051,19 +3039,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E21" s="19" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F21" s="19" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G21" s="19" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F21" s="19" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G21" s="19" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H21" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I21" s="19" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J21" s="19" t="s">
         <x:v>56</x:v>
@@ -3072,10 +3060,10 @@
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="L21" s="19" t="str">
-        <x:v>Evidencias equipo-a; revisión de Felipe pendiente</x:v>
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M21" s="19" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="N21" s="20" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -3101,31 +3089,31 @@
     </x:row>
     <x:row r="22" ht="27.950000762939453" customHeight="1">
       <x:c r="A22" s="22" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B22" s="22" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="D22" s="22" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="E22" s="22" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F22" s="22" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G22" s="22" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H22" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="22" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J22" s="22" t="s">
         <x:v>56</x:v>
@@ -3134,10 +3122,10 @@
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="L22" s="22" t="str">
-        <x:v>Evidencias equipo-a; revisión de Felipe pendiente</x:v>
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M22" s="22" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="N22" s="23" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -3163,10 +3151,10 @@
     </x:row>
     <x:row r="23" ht="27.950000762939453" customHeight="1">
       <x:c r="A23" s="19" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B23" s="19" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C23" s="19" t="s">
         <x:v>92</x:v>
@@ -3175,19 +3163,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E23" s="19" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F23" s="19" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G23" s="19" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F23" s="19" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G23" s="19" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H23" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I23" s="19" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J23" s="19" t="s">
         <x:v>56</x:v>
@@ -3196,10 +3184,10 @@
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="L23" s="19" t="str">
-        <x:v>Evidencias equipo-a; revisión de Felipe pendiente</x:v>
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M23" s="19" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="N23" s="20" t="str">
         <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
@@ -3225,10 +3213,10 @@
     </x:row>
     <x:row r="24" ht="27.950000762939453" customHeight="1">
       <x:c r="A24" s="22" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B24" s="22" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C24" s="22" t="s">
         <x:v>68</x:v>
@@ -3237,19 +3225,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E24" s="22" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F24" s="22" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G24" s="22" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H24" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I24" s="22" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="J24" s="22" t="s">
         <x:v>47</x:v>
@@ -3258,13 +3246,13 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L24" s="22" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="M24" s="22" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="N24" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="N24" s="20" t="str">
+        <x:v>REGRESION_LOCAL / ACEPTACION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O24" s="19"/>
       <x:c r="P24" s="19"/>
@@ -3287,10 +3275,10 @@
     </x:row>
     <x:row r="25" ht="27.950000762939453" customHeight="1">
       <x:c r="A25" s="19" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B25" s="19" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C25" s="19" t="s">
         <x:v>85</x:v>
@@ -3299,19 +3287,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="19" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F25" s="19" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G25" s="19" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F25" s="19" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G25" s="19" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H25" s="19">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="19" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="J25" s="19" t="s">
         <x:v>88</x:v>
@@ -3323,7 +3311,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="M25" s="19" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="N25" s="20" t="s">
         <x:v>42</x:v>
@@ -3349,10 +3337,10 @@
     </x:row>
     <x:row r="26" ht="27.950000762939453" customHeight="1">
       <x:c r="A26" s="22" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B26" s="22" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C26" s="22" t="s">
         <x:v>92</x:v>
@@ -3361,19 +3349,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E26" s="22" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F26" s="22" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G26" s="22" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F26" s="22" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G26" s="22" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="H26" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I26" s="22" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="J26" s="22" t="s">
         <x:v>56</x:v>
@@ -3382,13 +3370,13 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="L26" s="22" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M26" s="22" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="N26" s="20" t="str">
-        <x:v>TICKETS_LOCAL / CORRECCIONES_PENDIENTES</x:v>
+        <x:v>PARCIAL / E18_NOTE_PENDIENTE</x:v>
       </x:c>
       <x:c r="O26" s="19"/>
       <x:c r="P26" s="19"/>
@@ -3411,10 +3399,10 @@
     </x:row>
     <x:row r="27" ht="27.950000762939453" customHeight="1">
       <x:c r="A27" s="19" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B27" s="19" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C27" s="19" t="s">
         <x:v>92</x:v>
@@ -3423,19 +3411,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="19" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F27" s="19" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G27" s="19" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F27" s="19" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G27" s="19" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="H27" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="19" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="J27" s="19" t="s">
         <x:v>56</x:v>
@@ -3443,14 +3431,14 @@
       <x:c r="K27" s="19" t="str">
         <x:v>Catalina</x:v>
       </x:c>
-      <x:c r="L27" s="19" t="s">
-        <x:v>162</x:v>
+      <x:c r="L27" s="19" t="str">
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M27" s="19" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="N27" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="N27" s="20" t="str">
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O27" s="19"/>
       <x:c r="P27" s="19"/>
@@ -3473,10 +3461,10 @@
     </x:row>
     <x:row r="28" ht="27.950000762939453" customHeight="1">
       <x:c r="A28" s="22" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B28" s="22" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C28" s="22" t="s">
         <x:v>68</x:v>
@@ -3485,19 +3473,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E28" s="22" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F28" s="22" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G28" s="22" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F28" s="22" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G28" s="22" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="H28" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I28" s="22" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="J28" s="22" t="s">
         <x:v>47</x:v>
@@ -3509,10 +3497,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="M28" s="22" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="N28" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="N28" s="20" t="str">
+        <x:v>REGRESION_LOCAL / ACEPTACION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O28" s="19"/>
       <x:c r="P28" s="19"/>
@@ -3535,10 +3523,10 @@
     </x:row>
     <x:row r="29" ht="27.950000762939453" customHeight="1">
       <x:c r="A29" s="19" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B29" s="19" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C29" s="19" t="s">
         <x:v>85</x:v>
@@ -3547,19 +3535,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E29" s="19" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F29" s="19" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G29" s="19" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F29" s="19" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G29" s="19" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="H29" s="19">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="19" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="J29" s="19" t="s">
         <x:v>88</x:v>
@@ -3571,7 +3559,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="M29" s="19" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="N29" s="20" t="s">
         <x:v>42</x:v>
@@ -3597,10 +3585,10 @@
     </x:row>
     <x:row r="30" ht="27.950000762939453" customHeight="1">
       <x:c r="A30" s="22" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B30" s="22" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C30" s="22" t="s">
         <x:v>92</x:v>
@@ -3609,19 +3597,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E30" s="22" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F30" s="22" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G30" s="22" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H30" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I30" s="22" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="J30" s="22" t="s">
         <x:v>56</x:v>
@@ -3629,14 +3617,14 @@
       <x:c r="K30" s="22" t="str">
         <x:v>Catalina</x:v>
       </x:c>
-      <x:c r="L30" s="22" t="s">
-        <x:v>176</x:v>
+      <x:c r="L30" s="22" t="str">
+        <x:v>Guía 04 y evidencias/integracion; revisión humana pendiente</x:v>
       </x:c>
       <x:c r="M30" s="22" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="N30" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="N30" s="20" t="str">
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O30" s="19"/>
       <x:c r="P30" s="19"/>
@@ -3659,10 +3647,10 @@
     </x:row>
     <x:row r="31" ht="27.950000762939453" customHeight="1">
       <x:c r="A31" s="19" t="s">
-        <x:v>178</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B31" s="19" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C31" s="19" t="s">
         <x:v>92</x:v>
@@ -3671,19 +3659,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E31" s="19" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F31" s="19" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G31" s="19" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H31" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I31" s="19" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="J31" s="19" t="s">
         <x:v>56</x:v>
@@ -3692,13 +3680,13 @@
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="L31" s="19" t="s">
-        <x:v>180</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="M31" s="19" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="N31" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="N31" s="20" t="str">
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
       <x:c r="O31" s="19"/>
       <x:c r="P31" s="19"/>
@@ -3721,10 +3709,10 @@
     </x:row>
     <x:row r="32" ht="27.950000762939453" customHeight="1">
       <x:c r="A32" s="22" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B32" s="22" t="s">
-        <x:v>183</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C32" s="22" t="s">
         <x:v>68</x:v>
@@ -3733,19 +3721,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E32" s="22" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F32" s="22" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G32" s="22" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H32" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I32" s="22" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J32" s="22" t="s">
         <x:v>47</x:v>
@@ -3754,13 +3742,13 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L32" s="22" t="s">
-        <x:v>187</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="M32" s="22" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="N32" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="N32" s="20" t="str">
+        <x:v>REGRESION_LOCAL / ACEPTACION_PENDIENTE</x:v>
       </x:c>
       <x:c r="O32" s="19"/>
       <x:c r="P32" s="19"/>
@@ -3783,10 +3771,10 @@
     </x:row>
     <x:row r="33" ht="27.950000762939453" customHeight="1">
       <x:c r="A33" s="19" t="s">
-        <x:v>189</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B33" s="19" t="s">
-        <x:v>190</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C33" s="19" t="s">
         <x:v>79</x:v>
@@ -3795,19 +3783,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E33" s="19" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F33" s="19" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G33" s="19" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H33" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I33" s="19" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="J33" s="19" t="s">
         <x:v>47</x:v>
@@ -3816,10 +3804,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="L33" s="19" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="M33" s="19" t="s">
-        <x:v>192</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="N33" s="23" t="inlineStr">
         <x:is>
@@ -3847,10 +3835,10 @@
     </x:row>
     <x:row r="34" ht="27.950000762939453" customHeight="1">
       <x:c r="A34" s="22" t="s">
-        <x:v>193</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B34" s="22" t="s">
-        <x:v>194</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C34" s="22" t="s">
         <x:v>85</x:v>
@@ -3859,19 +3847,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E34" s="22" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="F34" s="22" t="s">
-        <x:v>195</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G34" s="22" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H34" s="22">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I34" s="22" t="s">
-        <x:v>196</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="J34" s="22" t="s">
         <x:v>88</x:v>
@@ -3883,7 +3871,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="M34" s="22" t="s">
-        <x:v>197</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="N34" s="20" t="s">
         <x:v>42</x:v>
@@ -3909,7 +3897,7 @@
     </x:row>
     <x:row r="35" ht="27.950000762939453" customHeight="1">
       <x:c r="A35" s="19" t="s">
-        <x:v>198</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B35" s="19" t="inlineStr">
         <x:is>
@@ -3920,22 +3908,22 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="D35" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E35" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F35" s="19" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G35" s="19" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H35" s="19">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="19" t="s">
-        <x:v>193</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J35" s="19" t="s">
         <x:v>56</x:v>
@@ -3944,10 +3932,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L35" s="19" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="M35" s="19" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="N35" s="20" t="s">
         <x:v>42</x:v>
@@ -3973,31 +3961,31 @@
     </x:row>
     <x:row r="36" ht="27.950000762939453" customHeight="1">
       <x:c r="A36" s="22" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B36" s="22" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C36" s="22" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D36" s="22" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E36" s="22" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F36" s="22" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G36" s="22" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H36" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I36" s="22" t="s">
-        <x:v>193</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J36" s="22" t="s">
         <x:v>47</x:v>
@@ -4006,10 +3994,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="L36" s="22" t="s">
-        <x:v>208</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="M36" s="22" t="s">
-        <x:v>209</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="N36" s="20" t="s">
         <x:v>42</x:v>
@@ -4035,31 +4023,31 @@
     </x:row>
     <x:row r="37" ht="27.950000762939453" customHeight="1">
       <x:c r="A37" s="19" t="s">
-        <x:v>210</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B37" s="19" t="s">
-        <x:v>211</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C37" s="19" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="D37" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E37" s="19" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F37" s="19" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G37" s="19" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H37" s="19">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I37" s="19" t="s">
-        <x:v>198</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="J37" s="19" t="s">
         <x:v>56</x:v>
@@ -4068,10 +4056,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="L37" s="19" t="s">
-        <x:v>212</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="M37" s="19" t="s">
-        <x:v>213</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="N37" s="23" t="inlineStr">
         <x:is>
@@ -4099,31 +4087,31 @@
     </x:row>
     <x:row r="38" ht="27.950000762939453" customHeight="1">
       <x:c r="A38" s="22" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B38" s="22" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C38" s="22" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D38" s="22" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="E38" s="22" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F38" s="22" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="B38" s="22" t="s">
+      <x:c r="G38" s="22" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D38" s="22" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="E38" s="22" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F38" s="22" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G38" s="22" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="H38" s="22">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I38" s="22" t="s">
-        <x:v>210</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="J38" s="22" t="s">
         <x:v>47</x:v>
@@ -4132,10 +4120,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L38" s="22" t="s">
-        <x:v>220</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="M38" s="22" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="N38" s="23" t="inlineStr">
         <x:is>
@@ -4163,43 +4151,43 @@
     </x:row>
     <x:row r="39" ht="27.950000762939453" customHeight="1">
       <x:c r="A39" s="19" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B39" s="19" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C39" s="19" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D39" s="19" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E39" s="19" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F39" s="19" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="B39" s="19" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="C39" s="19" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D39" s="19" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="E39" s="19" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F39" s="19" t="s">
-        <x:v>226</x:v>
-      </x:c>
       <x:c r="G39" s="19" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H39" s="19">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I39" s="19" t="s">
-        <x:v>227</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="J39" s="19" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="K39" s="19" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="L39" s="19" t="s">
-        <x:v>229</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="M39" s="19" t="s">
-        <x:v>230</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="N39" s="20" t="s">
         <x:v>42</x:v>
@@ -4225,10 +4213,10 @@
     </x:row>
     <x:row r="40" ht="27.950000762939453" customHeight="1">
       <x:c r="A40" s="22" t="s">
-        <x:v>231</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B40" s="22" t="s">
-        <x:v>232</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C40" s="22" t="s">
         <x:v>85</x:v>
@@ -4237,34 +4225,34 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="22" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F40" s="22" t="s">
-        <x:v>226</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G40" s="22" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H40" s="22">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I40" s="22" t="s">
-        <x:v>233</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="J40" s="22" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="K40" s="22" t="s">
-        <x:v>234</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="L40" s="22" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="M40" s="22" t="s">
-        <x:v>225</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="N40" s="23" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="O40" s="19"/>
       <x:c r="P40" s="19"/>
@@ -4287,25 +4275,25 @@
     </x:row>
     <x:row r="41" ht="27.950000762939453" customHeight="1">
       <x:c r="A41" s="19" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B41" s="19" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C41" s="19" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D41" s="19" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E41" s="19" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B41" s="19" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="C41" s="19" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D41" s="19" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="E41" s="19" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="F41" s="19" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G41" s="19" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H41" s="19">
         <x:v>18</x:v>
@@ -4313,13 +4301,13 @@
       <x:c r="I41" s="19"/>
       <x:c r="J41" s="19"/>
       <x:c r="K41" s="19" t="s">
-        <x:v>242</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="L41" s="19" t="s">
-        <x:v>243</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="M41" s="19" t="s">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="N41" s="20" t="str">
         <x:v>EN_CURSO</x:v>
@@ -4345,43 +4333,43 @@
     </x:row>
     <x:row r="42" ht="27.950000762939453" customHeight="1">
       <x:c r="A42" s="22" t="s">
-        <x:v>245</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B42" s="22" t="s">
-        <x:v>246</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C42" s="22" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D42" s="22" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E42" s="22" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F42" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G42" s="22" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H42" s="22">
         <x:v>18</x:v>
       </x:c>
       <x:c r="I42" s="22" t="s">
-        <x:v>237</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="J42" s="22" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="K42" s="22" t="s">
-        <x:v>242</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="L42" s="22" t="s">
-        <x:v>247</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="M42" s="22" t="s">
-        <x:v>248</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="N42" s="20" t="s">
         <x:v>42</x:v>
@@ -4407,31 +4395,31 @@
     </x:row>
     <x:row r="43" ht="27.950000762939453" customHeight="1">
       <x:c r="A43" s="19" t="s">
-        <x:v>249</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B43" s="19" t="s">
-        <x:v>250</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C43" s="19" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D43" s="19" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E43" s="19" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F43" s="19" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G43" s="19" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H43" s="19">
         <x:v>18</x:v>
       </x:c>
       <x:c r="I43" s="19" t="s">
-        <x:v>237</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="J43" s="19" t="s">
         <x:v>47</x:v>
@@ -4440,7 +4428,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="L43" s="19" t="s">
-        <x:v>251</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="M43" s="19" t="s">
         <x:v>85</x:v>
@@ -4469,25 +4457,25 @@
     </x:row>
     <x:row r="44" ht="27.950000762939453" customHeight="1">
       <x:c r="A44" s="22" t="s">
-        <x:v>252</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B44" s="22" t="s">
-        <x:v>253</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C44" s="22" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="D44" s="22" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E44" s="22" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F44" s="22" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="G44" s="22" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H44" s="22">
         <x:v>11</x:v>
@@ -4502,10 +4490,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L44" s="22" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="M44" s="22" t="s">
-        <x:v>255</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N44" s="20" t="str">
         <x:v>EN_CURSO</x:v>
@@ -4531,25 +4519,25 @@
     </x:row>
     <x:row r="45" ht="27.950000762939453" customHeight="1">
       <x:c r="A45" s="19" t="s">
-        <x:v>256</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B45" s="19" t="s">
-        <x:v>257</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C45" s="19" t="s">
-        <x:v>258</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D45" s="19" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E45" s="19" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F45" s="19" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="G45" s="19" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H45" s="19">
         <x:v>16</x:v>
@@ -4564,10 +4552,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="L45" s="19" t="s">
-        <x:v>259</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="M45" s="19" t="s">
-        <x:v>260</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="N45" s="20" t="str">
         <x:v>EN_CURSO</x:v>
@@ -4593,25 +4581,25 @@
     </x:row>
     <x:row r="46" ht="27.950000762939453" customHeight="1">
       <x:c r="A46" s="22" t="s">
-        <x:v>261</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B46" s="22" t="s">
-        <x:v>262</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C46" s="22" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D46" s="22" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E46" s="22" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F46" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G46" s="22" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H46" s="22">
         <x:v>18</x:v>
@@ -4622,10 +4610,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="L46" s="22" t="s">
-        <x:v>263</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="M46" s="22" t="s">
-        <x:v>264</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="N46" s="20" t="str">
         <x:v>EN_CURSO</x:v>
@@ -4669,7 +4657,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -4681,7 +4669,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="16" t="s">
-        <x:v>266</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B2" s="16"/>
       <x:c r="C2" s="16"/>
@@ -4706,68 +4694,68 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C4" s="27" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="E4" s="27" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F4" s="27" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="C4" s="27" t="s">
+      <x:c r="G4" s="27" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D4" s="27" t="s">
+      <x:c r="H4" s="27" t="s">
         <x:v>269</x:v>
-      </x:c>
-      <x:c r="E4" s="27" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="F4" s="27" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="G4" s="27" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H4" s="27" t="s">
-        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="28" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="s">
+      <x:c r="F5" s="28" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="C5" s="28" t="s">
+      <x:c r="H5" s="28" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="s">
-        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B6" s="29" t="s">
-        <x:v>282</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C6" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D6" s="29" t="s">
-        <x:v>283</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E6" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F6" s="29" t="inlineStr">
         <x:is>
@@ -4775,67 +4763,67 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="H6" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="28" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D7" s="28" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="E7" s="28" t="s">
-        <x:v>291</x:v>
-      </x:c>
       <x:c r="F7" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G7" s="28" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="H7" s="28" t="s">
-        <x:v>292</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="29" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D8" s="29" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="E8" s="29" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F8" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H8" s="29" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="B8" s="29" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="C8" s="29" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="D8" s="29" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="E8" s="29" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F8" s="29" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G8" s="29" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="H8" s="29" t="s">
-        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="28" t="s">
-        <x:v>298</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B9" s="28" t="inlineStr">
         <x:is>
@@ -4843,126 +4831,126 @@
         </x:is>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>299</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E9" s="28" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="F9" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="G9" s="28" t="s">
-        <x:v>300</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="H9" s="28" t="s">
-        <x:v>301</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="29" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H10" s="29" t="s">
         <x:v>302</x:v>
-      </x:c>
-      <x:c r="B10" s="29" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="H10" s="29" t="s">
-        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="28" t="s">
-        <x:v>307</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B11" s="28" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>309</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
-        <x:v>310</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E11" s="28" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="H11" s="28" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B12" s="29" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D12" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="E12" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F12" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G12" s="29" t="s">
-        <x:v>314</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="H12" s="29" t="s">
-        <x:v>315</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="28" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B13" s="28" t="s">
+      <x:c r="H13" s="28" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D13" s="28" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="H13" s="28" t="s">
-        <x:v>321</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4981,14 +4969,14 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>322</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="16" t="s">
-        <x:v>323</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B2" s="16"/>
       <x:c r="C2" s="16"/>
@@ -5000,98 +4988,98 @@
     </x:row>
     <x:row r="4" ht="33.95000076293945" customHeight="1">
       <x:c r="A4" s="27" t="s">
-        <x:v>324</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
-        <x:v>325</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C4" s="27" t="s">
-        <x:v>326</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="28" t="s">
-        <x:v>327</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B5" s="28" t="s">
-        <x:v>328</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C5" s="28" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="29" t="s">
-        <x:v>330</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B6" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C6" s="29" t="s">
-        <x:v>331</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="28" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B7" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C7" s="28" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="29" t="s">
-        <x:v>334</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B8" s="29" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C8" s="29" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="28" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B9" s="28" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>337</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="29" t="s">
-        <x:v>338</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B10" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="28" t="s">
-        <x:v>340</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B11" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>341</x:v>
+        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="29" t="s">
-        <x:v>342</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B12" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C12" s="29" t="inlineStr">
         <x:is>
@@ -5101,32 +5089,32 @@
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="28" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B13" s="28" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>344</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="29" t="s">
-        <x:v>345</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B14" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>346</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="28" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B15" s="28" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C15" s="28" t="inlineStr">
         <x:is>
@@ -5136,57 +5124,57 @@
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="29" t="s">
-        <x:v>348</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B16" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="28" t="s">
-        <x:v>350</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B17" s="28" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="29" t="s">
-        <x:v>352</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B18" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>353</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="28" t="s">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B19" s="28" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="29" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B20" s="29" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>358</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5205,7 +5193,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>359</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -5229,7 +5217,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="16" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B2" s="16"/>
       <x:c r="C2" s="16"/>
@@ -5278,173 +5266,173 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C4" s="27" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D4" s="27" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="E4" s="27" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F4" s="27" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="C4" s="27" t="s">
+      <x:c r="G4" s="27" t="s">
         <x:v>362</x:v>
-      </x:c>
-      <x:c r="D4" s="27" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="E4" s="27" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="F4" s="27" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="G4" s="27" t="s">
-        <x:v>366</x:v>
       </x:c>
       <x:c r="H4" s="27" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="I4" s="27" t="s">
-        <x:v>367</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="J4" s="27" t="s">
-        <x:v>258</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="K4" s="27" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="L4" s="27" t="s">
-        <x:v>368</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="M4" s="27" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="N4" s="27" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="O4" s="27" t="s">
-        <x:v>369</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="P4" s="27" t="s">
-        <x:v>370</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="Q4" s="27" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="R4" s="27" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="S4" s="27" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="T4" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="28" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
       <x:c r="I5" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="J5" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K5" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="L5" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M5" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="N5" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="O5" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="P5" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Q5" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="R5" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="S5" s="28" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="T5" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="29" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B6" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C6" s="29" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="D6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F6" s="29" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="G6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="I6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K6" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="L6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M6" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="N6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="O6" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="P6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="Q6" s="29" t="inlineStr">
         <x:is>
@@ -5452,571 +5440,571 @@
         </x:is>
       </x:c>
       <x:c r="R6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="S6" s="29" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="T6" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="28" t="s">
-        <x:v>379</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G7" s="28" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="H7" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="I7" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="J7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="L7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="N7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="O7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="P7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Q7" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R7" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="S7" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="T7" s="28" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="29" t="s">
-        <x:v>380</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H8" s="29" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="I8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="L8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="N8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="O8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="P8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Q8" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R8" s="29" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="S8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="T8" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="28" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B9" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E9" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H9" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="I9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J9" s="28" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="K9" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="L9" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="M9" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="N9" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="O9" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="P9" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="Q9" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="R9" s="28" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="K9" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="L9" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="M9" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="N9" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="O9" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="P9" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="Q9" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="R9" s="28" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="S9" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="T9" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="29" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B10" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H10" s="29" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="I10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K10" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="L10" s="29" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="N10" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="O10" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="P10" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="Q10" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="R10" s="29" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="S10" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="T10" s="29" t="s">
         <x:v>374</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="N10" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="O10" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="P10" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="Q10" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="R10" s="29" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="S10" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="T10" s="29" t="s">
-        <x:v>378</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="28" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="G11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H11" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="I11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K11" s="28" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="L11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M11" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="N11" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="O11" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="P11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="Q11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R11" s="28" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="S11" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="T11" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="29" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B12" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D12" s="29" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="H12" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="I12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="J12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="K12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="L12" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="M12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="N12" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="O12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="P12" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="Q12" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="R12" s="29" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="H12" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="I12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="K12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="L12" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="N12" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="O12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="P12" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="Q12" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="R12" s="29" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="S12" s="29" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="T12" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="28" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B13" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D13" s="28" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="H13" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="I13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="K13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="L13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="M13" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="N13" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="O13" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="P13" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="Q13" s="28" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="R13" s="28" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="H13" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="I13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="K13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="L13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="N13" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="O13" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="P13" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="Q13" s="28" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="R13" s="28" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="S13" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="T13" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="29" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B14" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E14" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="H14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="I14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="L14" s="29" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="N14" s="29" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="O14" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="P14" s="29" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="Q14" s="29" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="R14" s="29" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="S14" s="29" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="O14" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="P14" s="29" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="Q14" s="29" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="R14" s="29" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="S14" s="29" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="T14" s="29" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="28" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B15" s="28" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="G15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="H15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="I15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="K15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="L15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="M15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="N15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="O15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="P15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="Q15" s="28" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="R15" s="28" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="S15" s="28" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="H15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="I15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="K15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="L15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="N15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="O15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="P15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="Q15" s="28" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="R15" s="28" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="S15" s="28" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="T15" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6035,7 +6023,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -6057,7 +6045,7 @@
     </x:row>
     <x:row r="4" ht="33.95000076293945" customHeight="1">
       <x:c r="A4" s="27" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
         <x:v>6</x:v>
@@ -6066,7 +6054,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="27" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
@@ -6136,7 +6124,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -6150,7 +6138,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="D10" s="29" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -6161,10 +6149,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>391</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -6172,13 +6160,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C12" s="29" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D12" s="29" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
@@ -6186,13 +6174,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="28" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D13" s="28" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
@@ -6200,13 +6188,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C14" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D14" s="29" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
@@ -6214,13 +6202,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C15" s="28" t="s">
-        <x:v>395</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D15" s="28" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -6228,13 +6216,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C16" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D16" s="29" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -6242,13 +6230,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="28" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C17" s="28" t="s">
-        <x:v>397</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="D17" s="28" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -6256,13 +6244,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B18" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D18" s="29" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -6270,13 +6258,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="28" t="s">
-        <x:v>195</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C19" s="28" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D19" s="28" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
@@ -6284,13 +6272,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B20" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D20" s="29" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
@@ -6298,13 +6286,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="28" t="s">
-        <x:v>218</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C21" s="28" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D21" s="28" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -6312,13 +6300,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D22" s="29" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6340,7 +6328,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="15" t="s">
-        <x:v>400</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B1" s="15"/>
       <x:c r="C1" s="15"/>
@@ -6366,16 +6354,16 @@
     </x:row>
     <x:row r="4" ht="33.95000076293945" customHeight="1">
       <x:c r="A4" s="27" t="s">
-        <x:v>401</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B4" s="27" t="s">
-        <x:v>269</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C4" s="27" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D4" s="27" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E4" s="27" t="s">
         <x:v>12</x:v>
@@ -6386,242 +6374,242 @@
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="28" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="B5" s="28" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="s">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="s">
-        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="29" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="D6" s="29" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="E6" s="29" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B6" s="29" t="s">
+      <x:c r="F6" s="29" t="s">
         <x:v>410</x:v>
-      </x:c>
-      <x:c r="C6" s="29" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="D6" s="29" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="E6" s="29" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="F6" s="29" t="s">
-        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="28" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="s">
         <x:v>415</x:v>
-      </x:c>
-      <x:c r="B7" s="28" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="D7" s="28" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="E7" s="28" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="F7" s="28" t="s">
-        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="29" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B8" s="29" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C8" s="29" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="D8" s="29" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E8" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="F8" s="29" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="28" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B9" s="28" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="s">
-        <x:v>427</x:v>
-      </x:c>
       <x:c r="F9" s="28" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="29" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B10" s="29" t="s">
-        <x:v>277</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C10" s="29" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D10" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E10" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="F10" s="29" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="28" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B11" s="28" t="s">
-        <x:v>431</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C11" s="28" t="s">
-        <x:v>432</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E11" s="28" t="s">
-        <x:v>251</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="F11" s="28" t="s">
-        <x:v>433</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="29" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B12" s="29" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="D12" s="29" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B12" s="29" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="28" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B13" s="28" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C13" s="28" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D13" s="28" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E13" s="28" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F13" s="28" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="29" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B14" s="29" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D14" s="29" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="E14" s="29" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="B14" s="29" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>445</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="F14" s="29" t="s">
-        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="28" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B15" s="28" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="B15" s="28" t="s">
+      <x:c r="F15" s="28" t="s">
         <x:v>451</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="D15" s="28" t="s">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="29" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B16" s="29" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="D16" s="29" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="E16" s="29" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="B16" s="29" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>457</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="s">
-        <x:v>461</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
